--- a/Input/urbs_intertemporal_2050/2025.xlsx
+++ b/Input/urbs_intertemporal_2050/2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11192D6B-3D59-43F4-8F65-E6BA315F25EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FE3969-2F9C-45C7-91B7-5A9999E2B46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-5565" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="796" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -1885,17 +1885,7 @@
     <cellStyle name="Zelle überprüfen 4" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
     <cellStyle name="Zelle überprüfen 5" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <border>
         <top style="thin">
@@ -2140,247 +2130,14 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3203,13 +2960,13 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B11">
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B8:B11">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations xWindow="307" yWindow="342" count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Maximum commodity use per hour" prompt="For stock commodities, this value limits the energy use per hour (MW)._x000a_" sqref="F1" xr:uid="{737304EE-DF18-42D7-8893-3DE1D26EEDDE}"/>
@@ -3632,7 +3389,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G10" s="52">
         <v>5909565.7200000007</v>
@@ -3781,88 +3538,48 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="P2:XFD4">
-    <cfRule type="expression" dxfId="53" priority="24">
+  <conditionalFormatting sqref="A2:D13">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A14:XFD1048576 N12:XFD13">
-    <cfRule type="expression" dxfId="52" priority="36">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D13 F9:F13 F4:F6">
-    <cfRule type="expression" dxfId="33" priority="15">
+  <conditionalFormatting sqref="A1:XFD1 N12:XFD13 A14:XFD1048576">
+    <cfRule type="expression" dxfId="24" priority="36">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E4 E12:E13">
-    <cfRule type="expression" dxfId="32" priority="14">
+    <cfRule type="expression" dxfId="23" priority="14">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="expression" dxfId="31" priority="13">
+  <conditionalFormatting sqref="F4:F7">
+    <cfRule type="expression" dxfId="22" priority="12">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="expression" dxfId="30" priority="12">
+  <conditionalFormatting sqref="F9:F13">
+    <cfRule type="expression" dxfId="21" priority="15">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:M11">
-    <cfRule type="expression" dxfId="29" priority="11">
+  <conditionalFormatting sqref="F2:M2">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:I11">
-    <cfRule type="expression" dxfId="28" priority="10">
+    <cfRule type="expression" dxfId="19" priority="10">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12:M12">
-    <cfRule type="expression" dxfId="27" priority="9">
+  <conditionalFormatting sqref="G11:M12">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:M2">
-    <cfRule type="expression" dxfId="26" priority="8">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B9">
-    <cfRule type="expression" dxfId="25" priority="7">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="expression" dxfId="24" priority="6">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A13">
-    <cfRule type="expression" dxfId="23" priority="5">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="expression" dxfId="22" priority="4">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="21" priority="3">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="expression" dxfId="20" priority="2">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="expression" dxfId="19" priority="1">
+  <conditionalFormatting sqref="P2:XFD4">
+    <cfRule type="expression" dxfId="17" priority="24">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4510,56 +4227,68 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A35:XFD1048576 F8:XFD34">
-    <cfRule type="expression" dxfId="47" priority="74">
+  <conditionalFormatting sqref="A2:A5">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 F2:XFD4">
-    <cfRule type="expression" dxfId="46" priority="51">
+  <conditionalFormatting sqref="A20:A34">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:E1">
-    <cfRule type="dataBar" priority="108">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D35:E1048576">
-    <cfRule type="dataBar" priority="115">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:XFD7">
-    <cfRule type="expression" dxfId="36" priority="44">
+  <conditionalFormatting sqref="A1:XFD1">
+    <cfRule type="expression" dxfId="14" priority="51">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D19 A5 A6:C19 E6:E19 B2:C4 E2:E4">
-    <cfRule type="expression" dxfId="18" priority="35">
+  <conditionalFormatting sqref="A35:XFD1048576">
+    <cfRule type="expression" dxfId="13" priority="74">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:C25 C26 B27:C27">
-    <cfRule type="expression" dxfId="17" priority="26">
+  <conditionalFormatting sqref="B2:C4 E2:E4 A6:C19">
+    <cfRule type="expression" dxfId="12" priority="35">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20:C20 A26:A28 E23 E20">
-    <cfRule type="expression" dxfId="16" priority="27">
+  <conditionalFormatting sqref="B20:C25 C26">
+    <cfRule type="expression" dxfId="11" priority="26">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:C28">
+    <cfRule type="expression" dxfId="10" priority="22">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:C31">
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:C34">
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" dxfId="7" priority="14">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:E5">
-    <cfRule type="expression" dxfId="15" priority="20">
+    <cfRule type="expression" dxfId="5" priority="20">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D34">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4619,6 +4348,41 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D34">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:E1">
+    <cfRule type="dataBar" priority="108">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D2:E2 D3:D19">
     <cfRule type="dataBar" priority="34">
       <dataBar>
@@ -4675,6 +4439,15 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D35:E1048576">
+    <cfRule type="dataBar" priority="115">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E5">
     <cfRule type="dataBar" priority="21">
       <dataBar>
@@ -4687,6 +4460,11 @@
           <x14:id>{F4097541-4EFE-4D6C-86A7-318D200AE9A2}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E34">
+    <cfRule type="expression" dxfId="3" priority="19">
+      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E10">
@@ -4731,11 +4509,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E22">
-    <cfRule type="expression" dxfId="14" priority="25">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E23:E24">
     <cfRule type="dataBar" priority="29">
       <dataBar>
@@ -4748,11 +4521,6 @@
           <x14:id>{F1D82E9E-696A-4AF9-B2D0-23EA3BB9E23F}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24:E34">
-    <cfRule type="expression" dxfId="13" priority="19">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25:E26">
@@ -4797,31 +4565,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:C28">
-    <cfRule type="expression" dxfId="12" priority="22">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="expression" dxfId="11" priority="18">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29:A31">
-    <cfRule type="expression" dxfId="10" priority="17">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A34">
-    <cfRule type="expression" dxfId="9" priority="16">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29 B30:C30">
-    <cfRule type="expression" dxfId="8" priority="14">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E29">
     <cfRule type="dataBar" priority="13">
       <dataBar>
@@ -4862,16 +4605,6 @@
           <x14:id>{482D1302-BF25-4BED-A0AF-EE8C510D6066}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:C31">
-    <cfRule type="expression" dxfId="7" priority="11">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32 B33:C33">
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
@@ -4916,52 +4649,9 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34:C34">
-    <cfRule type="expression" dxfId="5" priority="6">
+  <conditionalFormatting sqref="F2:XFD34">
+    <cfRule type="expression" dxfId="2" priority="44">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20:A22">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D34">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D34">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D34">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}</x14:id>
-        </ext>
-      </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -5032,6 +4722,33 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>D15</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D20:D34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DF5A14F6-FAEA-436D-BC3B-FE807CD1C0A0}">
@@ -5303,36 +5020,6 @@
           </x14:cfRule>
           <xm:sqref>E34</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AD1BF178-371A-4438-B47F-1E6A4B5A3A75}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D20:D34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{97C8A1B8-CF7E-4BFD-B0AB-30267FAA4149}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>D20:D34</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -5411,7 +5098,7 @@
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <conditionalFormatting sqref="K1">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5711,7 +5398,7 @@
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <conditionalFormatting sqref="P1">
-    <cfRule type="expression" dxfId="34" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
